--- a/docs/downloads/经营分_津河省区__滨海片区_2026-10-19.xlsx
+++ b/docs/downloads/经营分_津河省区__滨海片区_2026-10-19.xlsx
@@ -12,7 +12,7 @@
     <sheet name="匹配异常" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'匹配异常'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1380,40 +1380,36 @@
           <t>滨海片区</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6691413193794799627</t>
+          <t>6881068386906834948</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津于家堡金融中心店）</t>
+          <t>维也纳酒店(5.0滨海新区海洋高新区旗舰店)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津于家堡金融中心店)</t>
+          <t>维也纳酒店(5.0滨海新区海洋高新区旗舰店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>87</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1429,7 +1425,7 @@
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
@@ -1441,7 +1437,7 @@
         <v>30</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="n">
         <v>20</v>
@@ -1475,17 +1471,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6601133369990318088</t>
+          <t>6691413193794799627</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津滨海开发区MSD第三大街店</t>
+          <t>维也纳酒店（天津于家堡金融中心店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津滨海开发区MSD第三大街店)</t>
+          <t>维也纳酒店(天津于家堡金融中心店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1563,22 +1559,22 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7103176063479449611</t>
+          <t>6601133369990318088</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>麗枫酒店（天津滨海新区福州道店）</t>
+          <t>麗枫酒店·天津滨海开发区MSD第三大街店</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津滨海新区福州道店)</t>
+          <t>麗枫酒店(天津滨海开发区MSD第三大街店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1651,17 +1647,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6745379904558237707</t>
+          <t>7103176063479449611</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7天优品Premium（天津大港胜利街店）</t>
+          <t>麗枫酒店（天津滨海新区福州道店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7天优品Premium(天津大港胜利街店)</t>
+          <t>麗枫酒店(天津滨海新区福州道店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1670,7 +1666,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1687,13 +1683,13 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
@@ -1739,29 +1735,29 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6729055458948024323</t>
+          <t>6745379904558237707</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IU酒店（天津滨海新区塘沽地铁站店）</t>
+          <t>7天优品Premium（天津大港胜利街店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IU酒店(天津滨海新区塘沽地铁站店)</t>
+          <t>7天优品Premium(天津大港胜利街店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>90</v>
       </c>
       <c r="I14" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1781,13 +1777,13 @@
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1827,17 +1823,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7556654794754557979</t>
+          <t>6729055458948024323</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津滨海新区大港油田步行街店）</t>
+          <t>IU酒店（天津滨海新区塘沽地铁站店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津滨海新区大港油田步行街店)</t>
+          <t>IU酒店(天津滨海新区塘沽地铁站店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1849,7 +1845,7 @@
         <v>90</v>
       </c>
       <c r="I15" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1863,19 +1859,19 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1915,33 +1911,33 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6678104788686686221</t>
+          <t>7556654794754557979</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津滨海开发区第三大街MSD店）</t>
+          <t>维也纳酒店（天津滨海新区大港油田步行街店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津滨海开发区第三大街MSD店)</t>
+          <t>维也纳酒店(天津滨海新区大港油田步行街店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1951,25 +1947,25 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P16" t="n">
         <v>30</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
         <v>30</v>
       </c>
       <c r="S16" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T16" t="n">
         <v>20</v>
@@ -2003,33 +1999,33 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7357212317975349263</t>
+          <t>6678104788686686221</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0天津保税海港店）</t>
+          <t>喆啡酒店（天津滨海开发区第三大街MSD店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津保税海港店)</t>
+          <t>喆啡酒店(天津滨海开发区第三大街MSD店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>92</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2039,13 +2035,13 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
@@ -2057,7 +2053,7 @@
         <v>30</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T17" t="n">
         <v>20</v>
@@ -2091,22 +2087,22 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7344969367873914891</t>
+          <t>7357212317975349263</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津滨海海洋高新区吾悦广场店</t>
+          <t>维也纳酒店（5.0天津保税海港店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>丽枫酒店(天津滨海西站吾悦广场店)</t>
+          <t>维也纳酒店(天津保税海港店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2179,33 +2175,33 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6601149668816603150</t>
+          <t>7344969367873914891</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津极地海洋公园滨海高铁站店</t>
+          <t>麗枫酒店·天津滨海海洋高新区吾悦广场店</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津极地海洋公园滨海高铁站店)</t>
+          <t>丽枫酒店(天津滨海西站吾悦广场店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>稳房源,提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2227,13 +2223,13 @@
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
       </c>
       <c r="S19" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T19" t="n">
         <v>20</v>
@@ -2267,17 +2263,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>6848943961499879439</t>
+          <t>6601149668816603150</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(天津中新生态城国家海博馆店)</t>
+          <t>麗枫酒店·天津极地海洋公园滨海高铁站店</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(天津中新生态城店)</t>
+          <t>麗枫酒店(天津极地海洋公园滨海高铁站店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2286,14 +2282,14 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -2303,25 +2299,25 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P20" t="n">
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T20" t="n">
         <v>20</v>
@@ -2355,17 +2351,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>6601141246784178190</t>
+          <t>6848943961499879439</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>锦江之星天津滨海极地海洋馆塘沽地铁站酒店</t>
+          <t>凯里亚德酒店(天津中新生态城国家海博馆店)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>锦江之星(天津滨海新区塘沽地铁站店)</t>
+          <t>凯里亚德酒店(天津中新生态城店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2377,11 +2373,11 @@
         <v>95</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2391,7 +2387,7 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
@@ -2403,7 +2399,7 @@
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2443,17 +2439,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7628436996242802714</t>
+          <t>6601141246784178190</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津滨海开发区MSD第二大街店)</t>
+          <t>锦江之星天津滨海极地海洋馆塘沽地铁站酒店</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津滨海开发区MSD第二大街店)</t>
+          <t>锦江之星(天津滨海新区塘沽地铁站店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2465,27 +2461,27 @@
         <v>95</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L22" t="n">
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
@@ -2531,17 +2527,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>6601155333769414660</t>
+          <t>7628436996242802714</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(天津中新生态城店)</t>
+          <t>麗枫酒店(天津滨海开发区MSD第二大街店)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(天津中新生态城店)</t>
+          <t>麗枫酒店(天津滨海开发区MSD第二大街店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2550,30 +2546,30 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I23" t="n">
         <v>5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
         <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N23" t="n">
         <v>30</v>
       </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P23" t="n">
         <v>30</v>
@@ -2619,29 +2615,29 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7371764058694879247</t>
+          <t>6601155333769414660</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>非繁城品酒店（天津极地海洋公园滨海高铁站）</t>
+          <t>维也纳3好酒店(天津中新生态城店)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>非繁城品酒店(天津滨海高铁站极地海洋馆店)</t>
+          <t>维也纳3好酒店(天津中新生态城店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2707,17 +2703,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7382105696239618067</t>
+          <t>7371764058694879247</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>凯里亚德酒店（3.0版天津滨海金街外滩公园店）</t>
+          <t>非繁城品酒店（天津极地海洋公园滨海高铁站）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(3.0版天津极地海洋公园外滩店)</t>
+          <t>非繁城品酒店(天津滨海高铁站极地海洋馆店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2726,14 +2722,14 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2743,13 +2739,13 @@
         <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N25" t="n">
         <v>30</v>
       </c>
       <c r="O25" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P25" t="n">
         <v>30</v>
@@ -2795,17 +2791,17 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7081635218968283168</t>
+          <t>7382105696239618067</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（天津滨海新区第五大街泰达永旺店）</t>
+          <t>凯里亚德酒店（3.0版天津滨海金街外滩公园店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(天津滨海新区第五大街泰达永旺店)</t>
+          <t>凯里亚德酒店(3.0版天津极地海洋公园外滩店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2814,7 +2810,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2831,7 +2827,7 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
@@ -2883,22 +2879,22 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>6917000177886693390</t>
+          <t>7081635218968283168</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（5.0版天津滨海新区生态城北塘古镇店）</t>
+          <t>维也纳3好酒店（天津滨海新区第五大街泰达永旺店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>维也纳国际酒店生态城(北塘古镇店)</t>
+          <t>维也纳3好酒店(天津滨海新区第五大街泰达永旺店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2909,7 +2905,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2919,19 +2915,19 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
       </c>
       <c r="O27" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P27" t="n">
         <v>30</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R27" t="n">
         <v>30</v>
@@ -2971,17 +2967,17 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>6601182611198969869</t>
+          <t>6917000177886693390</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>锦江之星天津中新生态城酒店</t>
+          <t>维也纳国际酒店（5.0版天津滨海新区生态城北塘古镇店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>锦江之星(天津中新生态城酒店)</t>
+          <t>维也纳国际酒店生态城(北塘古镇店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2997,7 +2993,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -3007,13 +3003,13 @@
         <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N28" t="n">
         <v>30</v>
       </c>
       <c r="O28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P28" t="n">
         <v>30</v>
@@ -3059,17 +3055,17 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>6601141776730294279</t>
+          <t>6601182611198969869</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>锦江之星天津滨海新区海洋高新区酒店</t>
+          <t>锦江之星天津中新生态城酒店</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>锦江之星(天津海洋高新区店)</t>
+          <t>锦江之星(天津中新生态城酒店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3081,11 +3077,11 @@
         <v>105</v>
       </c>
       <c r="I29" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3095,7 +3091,7 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N29" t="n">
         <v>30</v>
@@ -3107,7 +3103,7 @@
         <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R29" t="n">
         <v>30</v>
@@ -3147,33 +3143,33 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>6704924329206876168</t>
+          <t>6601141776730294279</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>凯里亚德酒店（天津于家堡金融中心店）</t>
+          <t>锦江之星天津滨海新区海洋高新区酒店</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(天津于家堡金融中心店)</t>
+          <t>锦江之星(天津海洋高新区店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3189,7 +3185,7 @@
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
@@ -3235,17 +3231,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>6823655529584379912</t>
+          <t>6704924329206876168</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（天津滨海新区塘沽地铁站店）</t>
+          <t>凯里亚德酒店（天津于家堡金融中心店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(天津滨海新区塘沽地铁站店)</t>
+          <t>凯里亚德酒店(天津于家堡金融中心店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3257,11 +3253,11 @@
         <v>110</v>
       </c>
       <c r="I31" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>提质量</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3277,13 +3273,13 @@
         <v>30</v>
       </c>
       <c r="O31" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P31" t="n">
         <v>30</v>
       </c>
       <c r="Q31" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R31" t="n">
         <v>30</v>
@@ -3323,33 +3319,33 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>6601148547385559053</t>
+          <t>6823655529584379912</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>锦江之星品尚天津塘沽地铁站中心北路酒店</t>
+          <t>维也纳国际酒店（天津滨海新区塘沽地铁站店）</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>锦江之星品尚(天津塘沽地铁站中心北路酒店)</t>
+          <t>维也纳国际酒店(天津滨海新区塘沽地铁站店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>110</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -3365,13 +3361,13 @@
         <v>30</v>
       </c>
       <c r="O32" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P32" t="n">
         <v>30</v>
       </c>
       <c r="Q32" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R32" t="n">
         <v>30</v>
@@ -3411,17 +3407,17 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>7168042609697064960</t>
+          <t>6601148547385559053</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>喆啡锐品酒店天津滨海塘沽火车站极地海洋馆店</t>
+          <t>锦江之星品尚天津塘沽地铁站中心北路酒店</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>喆啡锐品酒店(天津滨海塘沽火车站极地海洋馆店)</t>
+          <t>锦江之星品尚(天津塘沽地铁站中心北路酒店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3430,60 +3426,148 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>拿收益</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>10</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10</v>
+      </c>
+      <c r="M33" t="n">
+        <v>30</v>
+      </c>
+      <c r="N33" t="n">
+        <v>30</v>
+      </c>
+      <c r="O33" t="n">
+        <v>30</v>
+      </c>
+      <c r="P33" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>20</v>
+      </c>
+      <c r="R33" t="n">
+        <v>30</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="n">
+        <v>20</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>7249997748999555075</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>汇通百达网络科技（上海）有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>津河省区</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>滨海片区</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>7168042609697064960</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>喆啡锐品酒店天津滨海塘沽火车站极地海洋馆店</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>喆啡锐品酒店(天津滨海塘沽火车站极地海洋馆店)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>已认证</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>120</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>无</t>
         </is>
       </c>
-      <c r="K33" t="n">
-        <v>10</v>
-      </c>
-      <c r="L33" t="n">
-        <v>10</v>
-      </c>
-      <c r="M33" t="n">
-        <v>30</v>
-      </c>
-      <c r="N33" t="n">
-        <v>30</v>
-      </c>
-      <c r="O33" t="n">
-        <v>30</v>
-      </c>
-      <c r="P33" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>30</v>
-      </c>
-      <c r="R33" t="n">
-        <v>30</v>
-      </c>
-      <c r="S33" t="n">
-        <v>20</v>
-      </c>
-      <c r="T33" t="n">
-        <v>20</v>
-      </c>
-      <c r="U33" t="inlineStr">
+      <c r="K34" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" t="n">
+        <v>30</v>
+      </c>
+      <c r="N34" t="n">
+        <v>30</v>
+      </c>
+      <c r="O34" t="n">
+        <v>30</v>
+      </c>
+      <c r="P34" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>30</v>
+      </c>
+      <c r="R34" t="n">
+        <v>30</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="n">
+        <v>20</v>
+      </c>
+      <c r="U34" t="inlineStr">
         <is>
           <t>7249997748999555075</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>汇通百达网络科技（上海）有限公司</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V33"/>
-  <conditionalFormatting sqref="H2:H33">
+  <autoFilter ref="A1:V34"/>
+  <conditionalFormatting sqref="H2:H34">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -3495,7 +3579,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I33">
+  <conditionalFormatting sqref="I2:I34">
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
